--- a/files/temp_files/statement_2025_01.xlsx
+++ b/files/temp_files/statement_2025_01.xlsx
@@ -597,7 +597,7 @@
         <v>35</v>
       </c>
       <c r="C2">
-        <v>330.82</v>
+        <v>-330.82</v>
       </c>
       <c r="D2" t="s">
         <v>59</v>
@@ -611,7 +611,7 @@
         <v>36</v>
       </c>
       <c r="C3">
-        <v>225.27</v>
+        <v>-225.27</v>
       </c>
       <c r="D3" t="s">
         <v>60</v>
@@ -625,7 +625,7 @@
         <v>37</v>
       </c>
       <c r="C4">
-        <v>211.76</v>
+        <v>-211.76</v>
       </c>
       <c r="D4" t="s">
         <v>61</v>
@@ -639,7 +639,7 @@
         <v>38</v>
       </c>
       <c r="C5">
-        <v>228.41</v>
+        <v>-228.41</v>
       </c>
       <c r="D5" t="s">
         <v>59</v>
@@ -653,7 +653,7 @@
         <v>39</v>
       </c>
       <c r="C6">
-        <v>101.62</v>
+        <v>-101.62</v>
       </c>
       <c r="D6" t="s">
         <v>59</v>
@@ -667,7 +667,7 @@
         <v>40</v>
       </c>
       <c r="C7">
-        <v>11.37</v>
+        <v>-11.37</v>
       </c>
       <c r="D7" t="s">
         <v>62</v>
@@ -681,7 +681,7 @@
         <v>41</v>
       </c>
       <c r="C8">
-        <v>4.17</v>
+        <v>-4.17</v>
       </c>
       <c r="D8" t="s">
         <v>63</v>
@@ -695,7 +695,7 @@
         <v>41</v>
       </c>
       <c r="C9">
-        <v>26.01</v>
+        <v>-26.01</v>
       </c>
       <c r="D9" t="s">
         <v>63</v>
@@ -709,7 +709,7 @@
         <v>42</v>
       </c>
       <c r="C10">
-        <v>153.01</v>
+        <v>-153.01</v>
       </c>
       <c r="D10" t="s">
         <v>64</v>
@@ -723,7 +723,7 @@
         <v>38</v>
       </c>
       <c r="C11">
-        <v>191.64</v>
+        <v>-191.64</v>
       </c>
       <c r="D11" t="s">
         <v>59</v>
@@ -737,7 +737,7 @@
         <v>43</v>
       </c>
       <c r="C12">
-        <v>24.21</v>
+        <v>-24.21</v>
       </c>
       <c r="D12" t="s">
         <v>62</v>
@@ -751,7 +751,7 @@
         <v>44</v>
       </c>
       <c r="C13">
-        <v>137.16</v>
+        <v>-137.16</v>
       </c>
       <c r="D13" t="s">
         <v>65</v>
@@ -765,7 +765,7 @@
         <v>45</v>
       </c>
       <c r="C14">
-        <v>381.57</v>
+        <v>-381.57</v>
       </c>
       <c r="D14" t="s">
         <v>60</v>
@@ -779,7 +779,7 @@
         <v>43</v>
       </c>
       <c r="C15">
-        <v>60.87</v>
+        <v>-60.87</v>
       </c>
       <c r="D15" t="s">
         <v>62</v>
@@ -793,7 +793,7 @@
         <v>46</v>
       </c>
       <c r="C16">
-        <v>281.4</v>
+        <v>-281.4</v>
       </c>
       <c r="D16" t="s">
         <v>60</v>
@@ -821,7 +821,7 @@
         <v>41</v>
       </c>
       <c r="C18">
-        <v>42.98</v>
+        <v>-42.98</v>
       </c>
       <c r="D18" t="s">
         <v>63</v>
@@ -835,7 +835,7 @@
         <v>48</v>
       </c>
       <c r="C19">
-        <v>111.94</v>
+        <v>-111.94</v>
       </c>
       <c r="D19" t="s">
         <v>65</v>
@@ -849,7 +849,7 @@
         <v>49</v>
       </c>
       <c r="C20">
-        <v>148.12</v>
+        <v>-148.12</v>
       </c>
       <c r="D20" t="s">
         <v>64</v>
@@ -863,7 +863,7 @@
         <v>50</v>
       </c>
       <c r="C21">
-        <v>99.45999999999999</v>
+        <v>-99.45999999999999</v>
       </c>
       <c r="D21" t="s">
         <v>62</v>
@@ -891,7 +891,7 @@
         <v>51</v>
       </c>
       <c r="C23">
-        <v>95.87</v>
+        <v>-95.87</v>
       </c>
       <c r="D23" t="s">
         <v>64</v>
@@ -905,7 +905,7 @@
         <v>44</v>
       </c>
       <c r="C24">
-        <v>115.98</v>
+        <v>-115.98</v>
       </c>
       <c r="D24" t="s">
         <v>65</v>
@@ -919,7 +919,7 @@
         <v>52</v>
       </c>
       <c r="C25">
-        <v>111.39</v>
+        <v>-111.39</v>
       </c>
       <c r="D25" t="s">
         <v>61</v>
@@ -933,7 +933,7 @@
         <v>37</v>
       </c>
       <c r="C26">
-        <v>292.95</v>
+        <v>-292.95</v>
       </c>
       <c r="D26" t="s">
         <v>61</v>
@@ -961,7 +961,7 @@
         <v>35</v>
       </c>
       <c r="C28">
-        <v>228.3</v>
+        <v>-228.3</v>
       </c>
       <c r="D28" t="s">
         <v>59</v>
@@ -989,7 +989,7 @@
         <v>49</v>
       </c>
       <c r="C30">
-        <v>184.83</v>
+        <v>-184.83</v>
       </c>
       <c r="D30" t="s">
         <v>64</v>
@@ -1003,7 +1003,7 @@
         <v>43</v>
       </c>
       <c r="C31">
-        <v>86.15000000000001</v>
+        <v>-86.15000000000001</v>
       </c>
       <c r="D31" t="s">
         <v>62</v>
@@ -1017,7 +1017,7 @@
         <v>53</v>
       </c>
       <c r="C32">
-        <v>38.14</v>
+        <v>-38.14</v>
       </c>
       <c r="D32" t="s">
         <v>63</v>
@@ -1031,7 +1031,7 @@
         <v>39</v>
       </c>
       <c r="C33">
-        <v>348.21</v>
+        <v>-348.21</v>
       </c>
       <c r="D33" t="s">
         <v>59</v>
@@ -1045,7 +1045,7 @@
         <v>37</v>
       </c>
       <c r="C34">
-        <v>145.68</v>
+        <v>-145.68</v>
       </c>
       <c r="D34" t="s">
         <v>61</v>
@@ -1059,7 +1059,7 @@
         <v>42</v>
       </c>
       <c r="C35">
-        <v>95.01000000000001</v>
+        <v>-95.01000000000001</v>
       </c>
       <c r="D35" t="s">
         <v>64</v>
@@ -1073,7 +1073,7 @@
         <v>46</v>
       </c>
       <c r="C36">
-        <v>680.88</v>
+        <v>-680.88</v>
       </c>
       <c r="D36" t="s">
         <v>60</v>
@@ -1087,7 +1087,7 @@
         <v>53</v>
       </c>
       <c r="C37">
-        <v>31.13</v>
+        <v>-31.13</v>
       </c>
       <c r="D37" t="s">
         <v>63</v>
@@ -1101,7 +1101,7 @@
         <v>36</v>
       </c>
       <c r="C38">
-        <v>331.99</v>
+        <v>-331.99</v>
       </c>
       <c r="D38" t="s">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         <v>51</v>
       </c>
       <c r="C40">
-        <v>46.08</v>
+        <v>-46.08</v>
       </c>
       <c r="D40" t="s">
         <v>64</v>
@@ -1143,7 +1143,7 @@
         <v>51</v>
       </c>
       <c r="C41">
-        <v>121.86</v>
+        <v>-121.86</v>
       </c>
       <c r="D41" t="s">
         <v>64</v>
@@ -1157,7 +1157,7 @@
         <v>48</v>
       </c>
       <c r="C42">
-        <v>104.1</v>
+        <v>-104.1</v>
       </c>
       <c r="D42" t="s">
         <v>65</v>
@@ -1171,7 +1171,7 @@
         <v>44</v>
       </c>
       <c r="C43">
-        <v>60.69</v>
+        <v>-60.69</v>
       </c>
       <c r="D43" t="s">
         <v>65</v>
@@ -1185,7 +1185,7 @@
         <v>43</v>
       </c>
       <c r="C44">
-        <v>86.91</v>
+        <v>-86.91</v>
       </c>
       <c r="D44" t="s">
         <v>62</v>
@@ -1199,7 +1199,7 @@
         <v>48</v>
       </c>
       <c r="C45">
-        <v>100.52</v>
+        <v>-100.52</v>
       </c>
       <c r="D45" t="s">
         <v>65</v>
@@ -1213,7 +1213,7 @@
         <v>48</v>
       </c>
       <c r="C46">
-        <v>128.83</v>
+        <v>-128.83</v>
       </c>
       <c r="D46" t="s">
         <v>65</v>
@@ -1227,7 +1227,7 @@
         <v>55</v>
       </c>
       <c r="C47">
-        <v>84.88</v>
+        <v>-84.88</v>
       </c>
       <c r="D47" t="s">
         <v>65</v>
@@ -1241,7 +1241,7 @@
         <v>45</v>
       </c>
       <c r="C48">
-        <v>639.37</v>
+        <v>-639.37</v>
       </c>
       <c r="D48" t="s">
         <v>60</v>
@@ -1255,7 +1255,7 @@
         <v>55</v>
       </c>
       <c r="C49">
-        <v>51.34</v>
+        <v>-51.34</v>
       </c>
       <c r="D49" t="s">
         <v>65</v>
@@ -1269,7 +1269,7 @@
         <v>39</v>
       </c>
       <c r="C50">
-        <v>289.73</v>
+        <v>-289.73</v>
       </c>
       <c r="D50" t="s">
         <v>59</v>
@@ -1283,7 +1283,7 @@
         <v>36</v>
       </c>
       <c r="C51">
-        <v>194.77</v>
+        <v>-194.77</v>
       </c>
       <c r="D51" t="s">
         <v>60</v>
@@ -1297,7 +1297,7 @@
         <v>36</v>
       </c>
       <c r="C52">
-        <v>226.05</v>
+        <v>-226.05</v>
       </c>
       <c r="D52" t="s">
         <v>60</v>
@@ -1311,7 +1311,7 @@
         <v>52</v>
       </c>
       <c r="C53">
-        <v>110.16</v>
+        <v>-110.16</v>
       </c>
       <c r="D53" t="s">
         <v>61</v>
@@ -1325,7 +1325,7 @@
         <v>56</v>
       </c>
       <c r="C54">
-        <v>231.27</v>
+        <v>-231.27</v>
       </c>
       <c r="D54" t="s">
         <v>61</v>
@@ -1339,7 +1339,7 @@
         <v>57</v>
       </c>
       <c r="C55">
-        <v>39.13</v>
+        <v>-39.13</v>
       </c>
       <c r="D55" t="s">
         <v>63</v>
@@ -1353,7 +1353,7 @@
         <v>48</v>
       </c>
       <c r="C56">
-        <v>23.13</v>
+        <v>-23.13</v>
       </c>
       <c r="D56" t="s">
         <v>65</v>
@@ -1367,7 +1367,7 @@
         <v>48</v>
       </c>
       <c r="C57">
-        <v>21.51</v>
+        <v>-21.51</v>
       </c>
       <c r="D57" t="s">
         <v>65</v>
@@ -1381,7 +1381,7 @@
         <v>35</v>
       </c>
       <c r="C58">
-        <v>475.77</v>
+        <v>-475.77</v>
       </c>
       <c r="D58" t="s">
         <v>59</v>
@@ -1395,7 +1395,7 @@
         <v>42</v>
       </c>
       <c r="C59">
-        <v>165.52</v>
+        <v>-165.52</v>
       </c>
       <c r="D59" t="s">
         <v>64</v>
@@ -1409,7 +1409,7 @@
         <v>39</v>
       </c>
       <c r="C60">
-        <v>205.26</v>
+        <v>-205.26</v>
       </c>
       <c r="D60" t="s">
         <v>59</v>
@@ -1423,7 +1423,7 @@
         <v>42</v>
       </c>
       <c r="C61">
-        <v>152.67</v>
+        <v>-152.67</v>
       </c>
       <c r="D61" t="s">
         <v>64</v>
@@ -1437,7 +1437,7 @@
         <v>46</v>
       </c>
       <c r="C62">
-        <v>881.16</v>
+        <v>-881.16</v>
       </c>
       <c r="D62" t="s">
         <v>60</v>
@@ -1451,7 +1451,7 @@
         <v>44</v>
       </c>
       <c r="C63">
-        <v>125.71</v>
+        <v>-125.71</v>
       </c>
       <c r="D63" t="s">
         <v>65</v>
@@ -1465,7 +1465,7 @@
         <v>45</v>
       </c>
       <c r="C64">
-        <v>73.48</v>
+        <v>-73.48</v>
       </c>
       <c r="D64" t="s">
         <v>60</v>
@@ -1479,7 +1479,7 @@
         <v>37</v>
       </c>
       <c r="C65">
-        <v>246.88</v>
+        <v>-246.88</v>
       </c>
       <c r="D65" t="s">
         <v>61</v>
@@ -1493,7 +1493,7 @@
         <v>42</v>
       </c>
       <c r="C66">
-        <v>39.71</v>
+        <v>-39.71</v>
       </c>
       <c r="D66" t="s">
         <v>64</v>
@@ -1507,7 +1507,7 @@
         <v>44</v>
       </c>
       <c r="C67">
-        <v>100.48</v>
+        <v>-100.48</v>
       </c>
       <c r="D67" t="s">
         <v>65</v>
@@ -1521,7 +1521,7 @@
         <v>42</v>
       </c>
       <c r="C68">
-        <v>147.76</v>
+        <v>-147.76</v>
       </c>
       <c r="D68" t="s">
         <v>64</v>
@@ -1535,7 +1535,7 @@
         <v>40</v>
       </c>
       <c r="C69">
-        <v>92.90000000000001</v>
+        <v>-92.90000000000001</v>
       </c>
       <c r="D69" t="s">
         <v>62</v>
@@ -1549,7 +1549,7 @@
         <v>41</v>
       </c>
       <c r="C70">
-        <v>45.6</v>
+        <v>-45.6</v>
       </c>
       <c r="D70" t="s">
         <v>63</v>
@@ -1563,7 +1563,7 @@
         <v>40</v>
       </c>
       <c r="C71">
-        <v>13.71</v>
+        <v>-13.71</v>
       </c>
       <c r="D71" t="s">
         <v>62</v>
@@ -1591,7 +1591,7 @@
         <v>50</v>
       </c>
       <c r="C73">
-        <v>28.72</v>
+        <v>-28.72</v>
       </c>
       <c r="D73" t="s">
         <v>62</v>
@@ -1605,7 +1605,7 @@
         <v>49</v>
       </c>
       <c r="C74">
-        <v>34.24</v>
+        <v>-34.24</v>
       </c>
       <c r="D74" t="s">
         <v>64</v>
@@ -1619,7 +1619,7 @@
         <v>39</v>
       </c>
       <c r="C75">
-        <v>33.5</v>
+        <v>-33.5</v>
       </c>
       <c r="D75" t="s">
         <v>59</v>
@@ -1633,7 +1633,7 @@
         <v>35</v>
       </c>
       <c r="C76">
-        <v>199.28</v>
+        <v>-199.28</v>
       </c>
       <c r="D76" t="s">
         <v>59</v>
@@ -1647,7 +1647,7 @@
         <v>48</v>
       </c>
       <c r="C77">
-        <v>73.04000000000001</v>
+        <v>-73.04000000000001</v>
       </c>
       <c r="D77" t="s">
         <v>65</v>
@@ -1661,7 +1661,7 @@
         <v>38</v>
       </c>
       <c r="C78">
-        <v>359.25</v>
+        <v>-359.25</v>
       </c>
       <c r="D78" t="s">
         <v>59</v>
@@ -1675,7 +1675,7 @@
         <v>40</v>
       </c>
       <c r="C79">
-        <v>69.81999999999999</v>
+        <v>-69.81999999999999</v>
       </c>
       <c r="D79" t="s">
         <v>62</v>
@@ -1689,7 +1689,7 @@
         <v>56</v>
       </c>
       <c r="C80">
-        <v>121.11</v>
+        <v>-121.11</v>
       </c>
       <c r="D80" t="s">
         <v>61</v>
@@ -1703,7 +1703,7 @@
         <v>48</v>
       </c>
       <c r="C81">
-        <v>98.28</v>
+        <v>-98.28</v>
       </c>
       <c r="D81" t="s">
         <v>65</v>
@@ -1717,7 +1717,7 @@
         <v>39</v>
       </c>
       <c r="C82">
-        <v>51.59</v>
+        <v>-51.59</v>
       </c>
       <c r="D82" t="s">
         <v>59</v>
@@ -1731,7 +1731,7 @@
         <v>46</v>
       </c>
       <c r="C83">
-        <v>674.58</v>
+        <v>-674.58</v>
       </c>
       <c r="D83" t="s">
         <v>60</v>
@@ -1759,7 +1759,7 @@
         <v>42</v>
       </c>
       <c r="C85">
-        <v>186.71</v>
+        <v>-186.71</v>
       </c>
       <c r="D85" t="s">
         <v>64</v>
@@ -1773,7 +1773,7 @@
         <v>35</v>
       </c>
       <c r="C86">
-        <v>37.03</v>
+        <v>-37.03</v>
       </c>
       <c r="D86" t="s">
         <v>59</v>
@@ -1787,7 +1787,7 @@
         <v>35</v>
       </c>
       <c r="C87">
-        <v>346.98</v>
+        <v>-346.98</v>
       </c>
       <c r="D87" t="s">
         <v>59</v>
@@ -1801,7 +1801,7 @@
         <v>49</v>
       </c>
       <c r="C88">
-        <v>160.85</v>
+        <v>-160.85</v>
       </c>
       <c r="D88" t="s">
         <v>64</v>
@@ -1829,7 +1829,7 @@
         <v>43</v>
       </c>
       <c r="C90">
-        <v>19.89</v>
+        <v>-19.89</v>
       </c>
       <c r="D90" t="s">
         <v>62</v>
@@ -1843,7 +1843,7 @@
         <v>57</v>
       </c>
       <c r="C91">
-        <v>3.18</v>
+        <v>-3.18</v>
       </c>
       <c r="D91" t="s">
         <v>63</v>
@@ -1857,7 +1857,7 @@
         <v>43</v>
       </c>
       <c r="C92">
-        <v>92.09</v>
+        <v>-92.09</v>
       </c>
       <c r="D92" t="s">
         <v>62</v>
@@ -1871,7 +1871,7 @@
         <v>57</v>
       </c>
       <c r="C93">
-        <v>25.21</v>
+        <v>-25.21</v>
       </c>
       <c r="D93" t="s">
         <v>63</v>
@@ -1885,7 +1885,7 @@
         <v>36</v>
       </c>
       <c r="C94">
-        <v>660.64</v>
+        <v>-660.64</v>
       </c>
       <c r="D94" t="s">
         <v>60</v>
@@ -1913,7 +1913,7 @@
         <v>55</v>
       </c>
       <c r="C96">
-        <v>137.83</v>
+        <v>-137.83</v>
       </c>
       <c r="D96" t="s">
         <v>65</v>
@@ -1927,7 +1927,7 @@
         <v>41</v>
       </c>
       <c r="C97">
-        <v>25.53</v>
+        <v>-25.53</v>
       </c>
       <c r="D97" t="s">
         <v>63</v>
@@ -1941,7 +1941,7 @@
         <v>45</v>
       </c>
       <c r="C98">
-        <v>314.23</v>
+        <v>-314.23</v>
       </c>
       <c r="D98" t="s">
         <v>60</v>
@@ -1983,7 +1983,7 @@
         <v>43</v>
       </c>
       <c r="C101">
-        <v>69.54000000000001</v>
+        <v>-69.54000000000001</v>
       </c>
       <c r="D101" t="s">
         <v>62</v>
@@ -2011,7 +2011,7 @@
         <v>53</v>
       </c>
       <c r="C103">
-        <v>4.97</v>
+        <v>-4.97</v>
       </c>
       <c r="D103" t="s">
         <v>63</v>
@@ -2025,7 +2025,7 @@
         <v>43</v>
       </c>
       <c r="C104">
-        <v>24.33</v>
+        <v>-24.33</v>
       </c>
       <c r="D104" t="s">
         <v>62</v>
@@ -2039,7 +2039,7 @@
         <v>39</v>
       </c>
       <c r="C105">
-        <v>416.88</v>
+        <v>-416.88</v>
       </c>
       <c r="D105" t="s">
         <v>59</v>
@@ -2053,7 +2053,7 @@
         <v>42</v>
       </c>
       <c r="C106">
-        <v>169.49</v>
+        <v>-169.49</v>
       </c>
       <c r="D106" t="s">
         <v>64</v>
@@ -2067,7 +2067,7 @@
         <v>49</v>
       </c>
       <c r="C107">
-        <v>125.65</v>
+        <v>-125.65</v>
       </c>
       <c r="D107" t="s">
         <v>64</v>
@@ -2081,7 +2081,7 @@
         <v>52</v>
       </c>
       <c r="C108">
-        <v>246.47</v>
+        <v>-246.47</v>
       </c>
       <c r="D108" t="s">
         <v>61</v>
@@ -2095,7 +2095,7 @@
         <v>55</v>
       </c>
       <c r="C109">
-        <v>89.77</v>
+        <v>-89.77</v>
       </c>
       <c r="D109" t="s">
         <v>65</v>
@@ -2109,7 +2109,7 @@
         <v>40</v>
       </c>
       <c r="C110">
-        <v>53.99</v>
+        <v>-53.99</v>
       </c>
       <c r="D110" t="s">
         <v>62</v>
@@ -2123,7 +2123,7 @@
         <v>57</v>
       </c>
       <c r="C111">
-        <v>38.06</v>
+        <v>-38.06</v>
       </c>
       <c r="D111" t="s">
         <v>63</v>
@@ -2137,7 +2137,7 @@
         <v>55</v>
       </c>
       <c r="C112">
-        <v>61.57</v>
+        <v>-61.57</v>
       </c>
       <c r="D112" t="s">
         <v>65</v>
@@ -2151,7 +2151,7 @@
         <v>43</v>
       </c>
       <c r="C113">
-        <v>32.91</v>
+        <v>-32.91</v>
       </c>
       <c r="D113" t="s">
         <v>62</v>
@@ -2165,7 +2165,7 @@
         <v>35</v>
       </c>
       <c r="C114">
-        <v>317.6</v>
+        <v>-317.6</v>
       </c>
       <c r="D114" t="s">
         <v>59</v>
@@ -2193,7 +2193,7 @@
         <v>49</v>
       </c>
       <c r="C116">
-        <v>78.93000000000001</v>
+        <v>-78.93000000000001</v>
       </c>
       <c r="D116" t="s">
         <v>64</v>
@@ -2221,7 +2221,7 @@
         <v>41</v>
       </c>
       <c r="C118">
-        <v>22.58</v>
+        <v>-22.58</v>
       </c>
       <c r="D118" t="s">
         <v>63</v>
@@ -2235,7 +2235,7 @@
         <v>46</v>
       </c>
       <c r="C119">
-        <v>727.65</v>
+        <v>-727.65</v>
       </c>
       <c r="D119" t="s">
         <v>60</v>
@@ -2249,7 +2249,7 @@
         <v>41</v>
       </c>
       <c r="C120">
-        <v>24.39</v>
+        <v>-24.39</v>
       </c>
       <c r="D120" t="s">
         <v>63</v>
@@ -2277,7 +2277,7 @@
         <v>45</v>
       </c>
       <c r="C122">
-        <v>347.09</v>
+        <v>-347.09</v>
       </c>
       <c r="D122" t="s">
         <v>60</v>
@@ -2291,7 +2291,7 @@
         <v>50</v>
       </c>
       <c r="C123">
-        <v>74.29000000000001</v>
+        <v>-74.29000000000001</v>
       </c>
       <c r="D123" t="s">
         <v>62</v>
@@ -2305,7 +2305,7 @@
         <v>49</v>
       </c>
       <c r="C124">
-        <v>82.65000000000001</v>
+        <v>-82.65000000000001</v>
       </c>
       <c r="D124" t="s">
         <v>64</v>
@@ -2319,7 +2319,7 @@
         <v>56</v>
       </c>
       <c r="C125">
-        <v>60.64</v>
+        <v>-60.64</v>
       </c>
       <c r="D125" t="s">
         <v>61</v>
@@ -2333,7 +2333,7 @@
         <v>48</v>
       </c>
       <c r="C126">
-        <v>49.99</v>
+        <v>-49.99</v>
       </c>
       <c r="D126" t="s">
         <v>65</v>
@@ -2347,7 +2347,7 @@
         <v>50</v>
       </c>
       <c r="C127">
-        <v>53.68</v>
+        <v>-53.68</v>
       </c>
       <c r="D127" t="s">
         <v>62</v>
@@ -2361,7 +2361,7 @@
         <v>45</v>
       </c>
       <c r="C128">
-        <v>866.42</v>
+        <v>-866.42</v>
       </c>
       <c r="D128" t="s">
         <v>60</v>
@@ -2375,7 +2375,7 @@
         <v>36</v>
       </c>
       <c r="C129">
-        <v>424.19</v>
+        <v>-424.19</v>
       </c>
       <c r="D129" t="s">
         <v>60</v>
@@ -2389,7 +2389,7 @@
         <v>55</v>
       </c>
       <c r="C130">
-        <v>131.31</v>
+        <v>-131.31</v>
       </c>
       <c r="D130" t="s">
         <v>65</v>
@@ -2403,7 +2403,7 @@
         <v>43</v>
       </c>
       <c r="C131">
-        <v>35.87</v>
+        <v>-35.87</v>
       </c>
       <c r="D131" t="s">
         <v>62</v>
@@ -2417,7 +2417,7 @@
         <v>38</v>
       </c>
       <c r="C132">
-        <v>341.09</v>
+        <v>-341.09</v>
       </c>
       <c r="D132" t="s">
         <v>59</v>
@@ -2431,7 +2431,7 @@
         <v>39</v>
       </c>
       <c r="C133">
-        <v>235.06</v>
+        <v>-235.06</v>
       </c>
       <c r="D133" t="s">
         <v>59</v>
@@ -2445,7 +2445,7 @@
         <v>45</v>
       </c>
       <c r="C134">
-        <v>638.16</v>
+        <v>-638.16</v>
       </c>
       <c r="D134" t="s">
         <v>60</v>
@@ -2459,7 +2459,7 @@
         <v>45</v>
       </c>
       <c r="C135">
-        <v>157.4</v>
+        <v>-157.4</v>
       </c>
       <c r="D135" t="s">
         <v>60</v>
@@ -2473,7 +2473,7 @@
         <v>51</v>
       </c>
       <c r="C136">
-        <v>151.8</v>
+        <v>-151.8</v>
       </c>
       <c r="D136" t="s">
         <v>64</v>
@@ -2487,7 +2487,7 @@
         <v>38</v>
       </c>
       <c r="C137">
-        <v>332.26</v>
+        <v>-332.26</v>
       </c>
       <c r="D137" t="s">
         <v>59</v>
@@ -2501,7 +2501,7 @@
         <v>51</v>
       </c>
       <c r="C138">
-        <v>54.95</v>
+        <v>-54.95</v>
       </c>
       <c r="D138" t="s">
         <v>64</v>
@@ -2515,7 +2515,7 @@
         <v>44</v>
       </c>
       <c r="C139">
-        <v>41.17</v>
+        <v>-41.17</v>
       </c>
       <c r="D139" t="s">
         <v>65</v>
@@ -2557,7 +2557,7 @@
         <v>53</v>
       </c>
       <c r="C142">
-        <v>39.6</v>
+        <v>-39.6</v>
       </c>
       <c r="D142" t="s">
         <v>63</v>
@@ -2571,7 +2571,7 @@
         <v>46</v>
       </c>
       <c r="C143">
-        <v>641.55</v>
+        <v>-641.55</v>
       </c>
       <c r="D143" t="s">
         <v>60</v>
@@ -2585,7 +2585,7 @@
         <v>48</v>
       </c>
       <c r="C144">
-        <v>144.07</v>
+        <v>-144.07</v>
       </c>
       <c r="D144" t="s">
         <v>65</v>
@@ -2613,7 +2613,7 @@
         <v>35</v>
       </c>
       <c r="C146">
-        <v>198.31</v>
+        <v>-198.31</v>
       </c>
       <c r="D146" t="s">
         <v>59</v>
@@ -2641,7 +2641,7 @@
         <v>39</v>
       </c>
       <c r="C148">
-        <v>415</v>
+        <v>-415</v>
       </c>
       <c r="D148" t="s">
         <v>59</v>
@@ -2669,7 +2669,7 @@
         <v>38</v>
       </c>
       <c r="C150">
-        <v>391.76</v>
+        <v>-391.76</v>
       </c>
       <c r="D150" t="s">
         <v>59</v>
@@ -2683,7 +2683,7 @@
         <v>57</v>
       </c>
       <c r="C151">
-        <v>41.34</v>
+        <v>-41.34</v>
       </c>
       <c r="D151" t="s">
         <v>63</v>
@@ -2697,7 +2697,7 @@
         <v>38</v>
       </c>
       <c r="C152">
-        <v>33.19</v>
+        <v>-33.19</v>
       </c>
       <c r="D152" t="s">
         <v>59</v>
@@ -2711,7 +2711,7 @@
         <v>53</v>
       </c>
       <c r="C153">
-        <v>22.18</v>
+        <v>-22.18</v>
       </c>
       <c r="D153" t="s">
         <v>63</v>
@@ -2725,7 +2725,7 @@
         <v>43</v>
       </c>
       <c r="C154">
-        <v>27.36</v>
+        <v>-27.36</v>
       </c>
       <c r="D154" t="s">
         <v>62</v>
@@ -2739,7 +2739,7 @@
         <v>36</v>
       </c>
       <c r="C155">
-        <v>781.1</v>
+        <v>-781.1</v>
       </c>
       <c r="D155" t="s">
         <v>60</v>
@@ -2753,7 +2753,7 @@
         <v>53</v>
       </c>
       <c r="C156">
-        <v>49.51</v>
+        <v>-49.51</v>
       </c>
       <c r="D156" t="s">
         <v>63</v>
@@ -2767,7 +2767,7 @@
         <v>50</v>
       </c>
       <c r="C157">
-        <v>59.04</v>
+        <v>-59.04</v>
       </c>
       <c r="D157" t="s">
         <v>62</v>
@@ -2781,7 +2781,7 @@
         <v>38</v>
       </c>
       <c r="C158">
-        <v>244.66</v>
+        <v>-244.66</v>
       </c>
       <c r="D158" t="s">
         <v>59</v>
@@ -2795,7 +2795,7 @@
         <v>42</v>
       </c>
       <c r="C159">
-        <v>60.57</v>
+        <v>-60.57</v>
       </c>
       <c r="D159" t="s">
         <v>64</v>
@@ -2809,7 +2809,7 @@
         <v>44</v>
       </c>
       <c r="C160">
-        <v>95.52</v>
+        <v>-95.52</v>
       </c>
       <c r="D160" t="s">
         <v>65</v>
@@ -2823,7 +2823,7 @@
         <v>56</v>
       </c>
       <c r="C161">
-        <v>90.02</v>
+        <v>-90.02</v>
       </c>
       <c r="D161" t="s">
         <v>61</v>
@@ -2851,7 +2851,7 @@
         <v>37</v>
       </c>
       <c r="C163">
-        <v>263.41</v>
+        <v>-263.41</v>
       </c>
       <c r="D163" t="s">
         <v>61</v>
@@ -2865,7 +2865,7 @@
         <v>42</v>
       </c>
       <c r="C164">
-        <v>46.13</v>
+        <v>-46.13</v>
       </c>
       <c r="D164" t="s">
         <v>64</v>
@@ -2879,7 +2879,7 @@
         <v>46</v>
       </c>
       <c r="C165">
-        <v>521.22</v>
+        <v>-521.22</v>
       </c>
       <c r="D165" t="s">
         <v>60</v>
@@ -2893,7 +2893,7 @@
         <v>39</v>
       </c>
       <c r="C166">
-        <v>266.83</v>
+        <v>-266.83</v>
       </c>
       <c r="D166" t="s">
         <v>59</v>
@@ -2907,7 +2907,7 @@
         <v>35</v>
       </c>
       <c r="C167">
-        <v>494.63</v>
+        <v>-494.63</v>
       </c>
       <c r="D167" t="s">
         <v>59</v>
@@ -2921,7 +2921,7 @@
         <v>37</v>
       </c>
       <c r="C168">
-        <v>155.04</v>
+        <v>-155.04</v>
       </c>
       <c r="D168" t="s">
         <v>61</v>
@@ -2935,7 +2935,7 @@
         <v>44</v>
       </c>
       <c r="C169">
-        <v>68.33</v>
+        <v>-68.33</v>
       </c>
       <c r="D169" t="s">
         <v>65</v>
@@ -2949,7 +2949,7 @@
         <v>51</v>
       </c>
       <c r="C170">
-        <v>114.98</v>
+        <v>-114.98</v>
       </c>
       <c r="D170" t="s">
         <v>64</v>
@@ -2963,7 +2963,7 @@
         <v>42</v>
       </c>
       <c r="C171">
-        <v>156.95</v>
+        <v>-156.95</v>
       </c>
       <c r="D171" t="s">
         <v>64</v>
@@ -2991,7 +2991,7 @@
         <v>57</v>
       </c>
       <c r="C173">
-        <v>8.539999999999999</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="D173" t="s">
         <v>63</v>
@@ -3005,7 +3005,7 @@
         <v>57</v>
       </c>
       <c r="C174">
-        <v>17.38</v>
+        <v>-17.38</v>
       </c>
       <c r="D174" t="s">
         <v>63</v>
@@ -3019,7 +3019,7 @@
         <v>46</v>
       </c>
       <c r="C175">
-        <v>744.25</v>
+        <v>-744.25</v>
       </c>
       <c r="D175" t="s">
         <v>60</v>
@@ -3033,7 +3033,7 @@
         <v>52</v>
       </c>
       <c r="C176">
-        <v>265.62</v>
+        <v>-265.62</v>
       </c>
       <c r="D176" t="s">
         <v>61</v>
@@ -3047,7 +3047,7 @@
         <v>51</v>
       </c>
       <c r="C177">
-        <v>90.84999999999999</v>
+        <v>-90.84999999999999</v>
       </c>
       <c r="D177" t="s">
         <v>64</v>
@@ -3061,7 +3061,7 @@
         <v>41</v>
       </c>
       <c r="C178">
-        <v>22.87</v>
+        <v>-22.87</v>
       </c>
       <c r="D178" t="s">
         <v>63</v>
@@ -3075,7 +3075,7 @@
         <v>44</v>
       </c>
       <c r="C179">
-        <v>25.5</v>
+        <v>-25.5</v>
       </c>
       <c r="D179" t="s">
         <v>65</v>
@@ -3089,7 +3089,7 @@
         <v>51</v>
       </c>
       <c r="C180">
-        <v>120.4</v>
+        <v>-120.4</v>
       </c>
       <c r="D180" t="s">
         <v>64</v>
@@ -3103,7 +3103,7 @@
         <v>45</v>
       </c>
       <c r="C181">
-        <v>9.94</v>
+        <v>-9.94</v>
       </c>
       <c r="D181" t="s">
         <v>60</v>
@@ -3117,7 +3117,7 @@
         <v>42</v>
       </c>
       <c r="C182">
-        <v>162.28</v>
+        <v>-162.28</v>
       </c>
       <c r="D182" t="s">
         <v>64</v>
@@ -3145,7 +3145,7 @@
         <v>48</v>
       </c>
       <c r="C184">
-        <v>82.56</v>
+        <v>-82.56</v>
       </c>
       <c r="D184" t="s">
         <v>65</v>
@@ -3159,7 +3159,7 @@
         <v>52</v>
       </c>
       <c r="C185">
-        <v>92.3</v>
+        <v>-92.3</v>
       </c>
       <c r="D185" t="s">
         <v>61</v>
@@ -3173,7 +3173,7 @@
         <v>40</v>
       </c>
       <c r="C186">
-        <v>32</v>
+        <v>-32</v>
       </c>
       <c r="D186" t="s">
         <v>62</v>
@@ -3187,7 +3187,7 @@
         <v>46</v>
       </c>
       <c r="C187">
-        <v>298.25</v>
+        <v>-298.25</v>
       </c>
       <c r="D187" t="s">
         <v>60</v>
@@ -3201,7 +3201,7 @@
         <v>37</v>
       </c>
       <c r="C188">
-        <v>193.45</v>
+        <v>-193.45</v>
       </c>
       <c r="D188" t="s">
         <v>61</v>
@@ -3215,7 +3215,7 @@
         <v>57</v>
       </c>
       <c r="C189">
-        <v>15.99</v>
+        <v>-15.99</v>
       </c>
       <c r="D189" t="s">
         <v>63</v>
@@ -3257,7 +3257,7 @@
         <v>45</v>
       </c>
       <c r="C192">
-        <v>560.03</v>
+        <v>-560.03</v>
       </c>
       <c r="D192" t="s">
         <v>60</v>
@@ -3271,7 +3271,7 @@
         <v>36</v>
       </c>
       <c r="C193">
-        <v>749.84</v>
+        <v>-749.84</v>
       </c>
       <c r="D193" t="s">
         <v>60</v>
@@ -3285,7 +3285,7 @@
         <v>49</v>
       </c>
       <c r="C194">
-        <v>31.1</v>
+        <v>-31.1</v>
       </c>
       <c r="D194" t="s">
         <v>64</v>
@@ -3313,7 +3313,7 @@
         <v>39</v>
       </c>
       <c r="C196">
-        <v>389.06</v>
+        <v>-389.06</v>
       </c>
       <c r="D196" t="s">
         <v>59</v>
@@ -3327,7 +3327,7 @@
         <v>46</v>
       </c>
       <c r="C197">
-        <v>464.01</v>
+        <v>-464.01</v>
       </c>
       <c r="D197" t="s">
         <v>60</v>
@@ -3355,7 +3355,7 @@
         <v>46</v>
       </c>
       <c r="C199">
-        <v>883.39</v>
+        <v>-883.39</v>
       </c>
       <c r="D199" t="s">
         <v>60</v>
@@ -3369,7 +3369,7 @@
         <v>53</v>
       </c>
       <c r="C200">
-        <v>26.42</v>
+        <v>-26.42</v>
       </c>
       <c r="D200" t="s">
         <v>63</v>
@@ -3383,7 +3383,7 @@
         <v>41</v>
       </c>
       <c r="C201">
-        <v>48.12</v>
+        <v>-48.12</v>
       </c>
       <c r="D201" t="s">
         <v>63</v>
